--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N79_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N79_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>74.53276386984095</v>
+        <v>12.11157412884915</v>
       </c>
       <c r="D2" t="n">
-        <v>34.87869773424375</v>
+        <v>5.66778838181461</v>
       </c>
       <c r="E2" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F2" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>61.60010153622473</v>
+        <v>10.01001649963652</v>
       </c>
       <c r="D3" t="n">
-        <v>23.88522447514402</v>
+        <v>3.881348977210904</v>
       </c>
       <c r="E3" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F3" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>49.38396115949798</v>
+        <v>8.024893688418421</v>
       </c>
       <c r="D4" t="n">
-        <v>22.23662697690433</v>
+        <v>3.613451883746954</v>
       </c>
       <c r="E4" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F4" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>73.40886481406123</v>
+        <v>11.92894053228495</v>
       </c>
       <c r="D5" t="n">
-        <v>39.34836446950943</v>
+        <v>6.394109226295282</v>
       </c>
       <c r="E5" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F5" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>56.35628307032289</v>
+        <v>9.15789599892747</v>
       </c>
       <c r="D6" t="n">
-        <v>16.81351113824006</v>
+        <v>2.732195559964009</v>
       </c>
       <c r="E6" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F6" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>42.64364586149834</v>
+        <v>6.92959245249348</v>
       </c>
       <c r="D7" t="n">
-        <v>4.906830799469868</v>
+        <v>0.7973600049138536</v>
       </c>
       <c r="E7" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F7" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>50.42682297484343</v>
+        <v>8.194358733412058</v>
       </c>
       <c r="D8" t="n">
-        <v>11.5233201864078</v>
+        <v>1.872539530291268</v>
       </c>
       <c r="E8" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F8" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>73.07699748351833</v>
+        <v>11.87501209107173</v>
       </c>
       <c r="D9" t="n">
-        <v>63.36685379852039</v>
+        <v>10.29711374225956</v>
       </c>
       <c r="E9" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F9" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>41.8285846204747</v>
+        <v>6.797145000827139</v>
       </c>
       <c r="D10" t="n">
-        <v>9.703748153383497</v>
+        <v>1.576859074924818</v>
       </c>
       <c r="E10" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F10" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>33.06115395387194</v>
+        <v>5.37243751750419</v>
       </c>
       <c r="D11" t="n">
-        <v>9.190717549291492</v>
+        <v>1.493491601759867</v>
       </c>
       <c r="E11" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F11" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>21.52324325003088</v>
+        <v>3.497527028130019</v>
       </c>
       <c r="D12" t="n">
-        <v>25.00756299259788</v>
+        <v>4.063728986297155</v>
       </c>
       <c r="E12" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F12" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>16.55309233124093</v>
+        <v>2.689877503826651</v>
       </c>
       <c r="D13" t="n">
-        <v>20.49249331848129</v>
+        <v>3.33003016425321</v>
       </c>
       <c r="E13" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F13" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>24.23020552249575</v>
+        <v>3.937408397405559</v>
       </c>
       <c r="D14" t="n">
-        <v>18.48615293159202</v>
+        <v>3.003999851383704</v>
       </c>
       <c r="E14" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F14" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>17.69180601295413</v>
+        <v>2.874918477105047</v>
       </c>
       <c r="D15" t="n">
-        <v>18.23116599487431</v>
+        <v>2.962564474167075</v>
       </c>
       <c r="E15" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F15" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>11.74842919794409</v>
+        <v>1.909119744665914</v>
       </c>
       <c r="D16" t="n">
-        <v>12.05195173839909</v>
+        <v>1.958442157489852</v>
       </c>
       <c r="E16" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F16" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>32.48947129774371</v>
+        <v>5.279539085883353</v>
       </c>
       <c r="D17" t="n">
-        <v>44.98278304587584</v>
+        <v>7.309702244954824</v>
       </c>
       <c r="E17" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F17" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>9.219544457292887</v>
+        <v>1.498175974310094</v>
       </c>
       <c r="D18" t="n">
-        <v>13.33359947653271</v>
+        <v>2.166709914936566</v>
       </c>
       <c r="E18" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F18" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>25.91030689914463</v>
+        <v>4.210424871111002</v>
       </c>
       <c r="D19" t="n">
-        <v>37.23271094299714</v>
+        <v>6.050315528237036</v>
       </c>
       <c r="E19" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F19" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>7.395588644926021</v>
+        <v>1.201783154800478</v>
       </c>
       <c r="D20" t="n">
-        <v>12.66996164462502</v>
+        <v>2.058868767251565</v>
       </c>
       <c r="E20" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F20" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>48.65764566300013</v>
+        <v>7.906867420237521</v>
       </c>
       <c r="D21" t="n">
-        <v>58.8560414023933</v>
+        <v>9.564106727888912</v>
       </c>
       <c r="E21" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F21" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>23.67404277458101</v>
+        <v>3.847031950869414</v>
       </c>
       <c r="D22" t="n">
-        <v>10.34047327514878</v>
+        <v>1.680326907211677</v>
       </c>
       <c r="E22" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F22" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>13.35610473149297</v>
+        <v>2.170367018867609</v>
       </c>
       <c r="D23" t="n">
-        <v>28.02887412665566</v>
+        <v>4.554692045581545</v>
       </c>
       <c r="E23" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F23" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>12.93294006259863</v>
+        <v>2.101602760172277</v>
       </c>
       <c r="D24" t="n">
-        <v>4.458770587358297</v>
+        <v>0.7245502204457233</v>
       </c>
       <c r="E24" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F24" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>18.43381554522979</v>
+        <v>2.995495026099841</v>
       </c>
       <c r="D25" t="n">
-        <v>2.329911191088541</v>
+        <v>0.378610568551888</v>
       </c>
       <c r="E25" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F25" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>8.910044269749104</v>
+        <v>1.447882193834229</v>
       </c>
       <c r="D26" t="n">
-        <v>7.782913179202732</v>
+        <v>1.264723391620444</v>
       </c>
       <c r="E26" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F26" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>16.02291497711121</v>
+        <v>2.603723683780572</v>
       </c>
       <c r="D27" t="n">
-        <v>17.78564313041561</v>
+        <v>2.890167008692537</v>
       </c>
       <c r="E27" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F27" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>10.06828030698219</v>
+        <v>1.636095549884606</v>
       </c>
       <c r="D28" t="n">
-        <v>10.19732080315707</v>
+        <v>1.657064630513024</v>
       </c>
       <c r="E28" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F28" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>35.90629666045776</v>
+        <v>5.834773207324385</v>
       </c>
       <c r="D29" t="n">
-        <v>47.13165558794253</v>
+        <v>7.658894033040662</v>
       </c>
       <c r="E29" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F29" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>52.68226441499734</v>
+        <v>8.560867967437069</v>
       </c>
       <c r="D30" t="n">
-        <v>57.60166738649338</v>
+        <v>9.360270950305175</v>
       </c>
       <c r="E30" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F30" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>18.97732565165305</v>
+        <v>3.08381541839362</v>
       </c>
       <c r="D31" t="n">
-        <v>5.659174102418839</v>
+        <v>0.9196157916430614</v>
       </c>
       <c r="E31" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F31" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>17.39318702600302</v>
+        <v>2.826392891725491</v>
       </c>
       <c r="D32" t="n">
-        <v>34.02492546548756</v>
+        <v>5.529050388141729</v>
       </c>
       <c r="E32" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F32" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>6.761193279880517</v>
+        <v>1.098693907980584</v>
       </c>
       <c r="D33" t="n">
-        <v>15.25113878628572</v>
+        <v>2.47831005277143</v>
       </c>
       <c r="E33" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F33" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>9.732536786699026</v>
+        <v>1.581537227838592</v>
       </c>
       <c r="D34" t="n">
-        <v>23.70623022672521</v>
+        <v>3.852262411842847</v>
       </c>
       <c r="E34" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F34" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>11.94549908332466</v>
+        <v>1.941143601040258</v>
       </c>
       <c r="D35" t="n">
-        <v>13.61721286307736</v>
+        <v>2.212797090250071</v>
       </c>
       <c r="E35" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F35" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>38.67545837269014</v>
+        <v>6.284761985562148</v>
       </c>
       <c r="D36" t="n">
-        <v>39.34582434901738</v>
+        <v>6.393696456715325</v>
       </c>
       <c r="E36" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F36" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>13.17816838807991</v>
+        <v>2.141452363062985</v>
       </c>
       <c r="D37" t="n">
-        <v>12.8524830799048</v>
+        <v>2.088528500484531</v>
       </c>
       <c r="E37" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F37" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>27.57897065595582</v>
+        <v>4.481582731592821</v>
       </c>
       <c r="D38" t="n">
-        <v>23.47279151020532</v>
+        <v>3.814328620408365</v>
       </c>
       <c r="E38" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F38" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>53.48251108044195</v>
+        <v>8.690908050571817</v>
       </c>
       <c r="D39" t="n">
-        <v>31.30891224009519</v>
+        <v>5.087698239015468</v>
       </c>
       <c r="E39" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F39" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1696,16 +1696,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>58.80843342644835</v>
+        <v>9.556370431797857</v>
       </c>
       <c r="D40" t="n">
-        <v>29.18359348007037</v>
+        <v>4.742333940511435</v>
       </c>
       <c r="E40" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F40" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>37.53310411761332</v>
+        <v>6.099129419112165</v>
       </c>
       <c r="D41" t="n">
-        <v>37.05034962207585</v>
+        <v>6.020681813587326</v>
       </c>
       <c r="E41" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F41" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1760,16 +1760,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>36.71209993562127</v>
+        <v>5.965716239538456</v>
       </c>
       <c r="D42" t="n">
-        <v>41.73485176159728</v>
+        <v>6.781913411259559</v>
       </c>
       <c r="E42" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F42" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1792,16 +1792,16 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>49.63607936447523</v>
+        <v>8.065862896727225</v>
       </c>
       <c r="D43" t="n">
-        <v>27.985316435224</v>
+        <v>4.5476139207239</v>
       </c>
       <c r="E43" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F43" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>46.76736893817887</v>
+        <v>7.599697452454066</v>
       </c>
       <c r="D44" t="n">
-        <v>34.2142639917655</v>
+        <v>5.559817898661894</v>
       </c>
       <c r="E44" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F44" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1856,16 +1856,16 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>46.2436136950607</v>
+        <v>7.514587225447364</v>
       </c>
       <c r="D45" t="n">
-        <v>19.79004986462479</v>
+        <v>3.215883103001528</v>
       </c>
       <c r="E45" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F45" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1888,16 +1888,16 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>19.16054618565323</v>
+        <v>3.11358875516865</v>
       </c>
       <c r="D46" t="n">
-        <v>38.91654111357578</v>
+        <v>6.323937930956065</v>
       </c>
       <c r="E46" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F46" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1920,16 +1920,16 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>59.05106242291198</v>
+        <v>9.595797643723197</v>
       </c>
       <c r="D47" t="n">
-        <v>19.18185944283745</v>
+        <v>3.117052159461085</v>
       </c>
       <c r="E47" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F47" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1952,16 +1952,16 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>56.12398331723963</v>
+        <v>9.12014728905144</v>
       </c>
       <c r="D48" t="n">
-        <v>16.49810750856698</v>
+        <v>2.680942470142134</v>
       </c>
       <c r="E48" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F48" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1984,16 +1984,16 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>71.70177384754057</v>
+        <v>11.65153825022534</v>
       </c>
       <c r="D49" t="n">
-        <v>10.39452658189918</v>
+        <v>1.689110569558617</v>
       </c>
       <c r="E49" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F49" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>73.36612449947977</v>
+        <v>11.92199523116546</v>
       </c>
       <c r="D50" t="n">
-        <v>3.62748116519276</v>
+        <v>0.5894656893438235</v>
       </c>
       <c r="E50" t="n">
-        <v>20.84431588028329</v>
+        <v>3.387201330546036</v>
       </c>
       <c r="F50" t="n">
-        <v>14.97404579412089</v>
+        <v>2.433282441544645</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
